--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEW_JERSEY_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEW_JERSEY_2011.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C93">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C395">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C489">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C741">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C773">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C860">
